--- a/design/蛋仔--大富翁--黑市表.xlsx
+++ b/design/蛋仔--大富翁--黑市表.xlsx
@@ -5,16 +5,19 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\策划文档\大富翁\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\eggitor\1_开发中\大富翁\monopoly\design\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CB9B9C2-FAC9-4345-B74F-CDC2F5247D79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5810EA8F-7B44-4848-B781-FC103C7B7A5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$2:$G$2</definedName>
+  </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -25,17 +28,13 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="45">
   <si>
     <t>字符串</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>整数</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>广告</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -272,11 +271,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -567,25 +565,25 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>44</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
@@ -615,592 +613,592 @@
       <c r="A3" s="1">
         <v>1</v>
       </c>
-      <c r="B3" s="3">
-        <v>2001</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>8</v>
+      <c r="B3" s="2">
+        <v>2003</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>7</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>2</v>
       </c>
       <c r="F3" s="2">
-        <v>1</v>
+        <v>2500</v>
       </c>
       <c r="G3" s="2">
-        <v>999</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>2</v>
       </c>
-      <c r="B4" s="3">
-        <v>2003</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>8</v>
+      <c r="B4" s="2">
+        <v>2005</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>7</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F4" s="2">
-        <v>5000</v>
+        <v>2500</v>
       </c>
       <c r="G4" s="2">
-        <v>999</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>3</v>
       </c>
-      <c r="B5" s="3">
-        <v>2005</v>
-      </c>
-      <c r="C5" s="3" t="s">
+      <c r="B5" s="2">
+        <v>2006</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D5" s="3" t="s">
-        <v>8</v>
+      <c r="D5" s="2" t="s">
+        <v>7</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F5" s="2">
-        <v>5000</v>
+        <v>2500</v>
       </c>
       <c r="G5" s="2">
-        <v>999</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>4</v>
       </c>
-      <c r="B6" s="3">
-        <v>2006</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>8</v>
+      <c r="B6" s="2">
+        <v>2002</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>7</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F6" s="2">
         <v>5000</v>
       </c>
       <c r="G6" s="2">
-        <v>999</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>5</v>
       </c>
-      <c r="B7" s="3">
+      <c r="B7" s="2">
         <v>2004</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>8</v>
+      <c r="C7" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>7</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F7" s="2">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="G7" s="2">
-        <v>999</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>6</v>
       </c>
-      <c r="B8" s="3">
-        <v>2002</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>8</v>
+      <c r="B8" s="2">
+        <v>2012</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>7</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F8" s="2">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="G8" s="2">
-        <v>999</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>7</v>
       </c>
-      <c r="B9" s="3">
-        <v>2007</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>8</v>
+      <c r="B9" s="2">
+        <v>2001</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>7</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F9" s="2">
         <v>100</v>
       </c>
       <c r="G9" s="2">
-        <v>999</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <v>8</v>
       </c>
-      <c r="B10" s="3">
-        <v>2009</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>8</v>
+      <c r="B10" s="2">
+        <v>2007</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>7</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F10" s="2">
         <v>100</v>
       </c>
       <c r="G10" s="2">
-        <v>999</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <v>9</v>
       </c>
-      <c r="B11" s="3">
-        <v>2012</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>8</v>
+      <c r="B11" s="2">
+        <v>2008</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>7</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F11" s="2">
         <v>100</v>
       </c>
       <c r="G11" s="2">
-        <v>999</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <v>10</v>
       </c>
-      <c r="B12" s="3">
-        <v>2008</v>
-      </c>
-      <c r="C12" s="3" t="s">
+      <c r="B12" s="2">
+        <v>2009</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>8</v>
+      <c r="D12" s="2" t="s">
+        <v>7</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F12" s="2">
         <v>5</v>
       </c>
       <c r="G12" s="2">
-        <v>999</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <v>11</v>
       </c>
-      <c r="B13" s="3">
+      <c r="B13" s="2">
         <v>2010</v>
       </c>
-      <c r="C13" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>8</v>
+      <c r="C13" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>7</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F13" s="2">
         <v>5</v>
       </c>
       <c r="G13" s="2">
-        <v>999</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
         <v>12</v>
       </c>
-      <c r="B14" s="3">
-        <v>2011</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>8</v>
+      <c r="B14" s="2">
+        <v>2013</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>7</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F14" s="2">
         <v>5</v>
       </c>
       <c r="G14" s="2">
-        <v>999</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
         <v>13</v>
       </c>
-      <c r="B15" s="3">
-        <v>2013</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>8</v>
+      <c r="B15" s="2">
+        <v>2017</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>7</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F15" s="2">
         <v>10</v>
       </c>
       <c r="G15" s="2">
-        <v>999</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
         <v>14</v>
       </c>
-      <c r="B16" s="3">
-        <v>2015</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>8</v>
+      <c r="B16" s="2">
+        <v>2018</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>7</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F16" s="2">
         <v>10</v>
       </c>
       <c r="G16" s="2">
-        <v>999</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
         <v>15</v>
       </c>
-      <c r="B17" s="3">
-        <v>2016</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>8</v>
+      <c r="B17" s="2">
+        <v>2019</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>7</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F17" s="2">
         <v>10</v>
       </c>
       <c r="G17" s="2">
-        <v>999</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
         <v>16</v>
       </c>
-      <c r="B18" s="3">
-        <v>2017</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>8</v>
+      <c r="B18" s="2">
+        <v>2015</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>7</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F18" s="2">
         <v>20</v>
       </c>
       <c r="G18" s="2">
-        <v>999</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
         <v>17</v>
       </c>
-      <c r="B19" s="3">
-        <v>2018</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>8</v>
+      <c r="B19" s="2">
+        <v>2016</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>7</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F19" s="2">
         <v>20</v>
       </c>
       <c r="G19" s="2">
-        <v>999</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
         <v>18</v>
       </c>
-      <c r="B20" s="3">
-        <v>2019</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>8</v>
+      <c r="B20" s="2">
+        <v>2011</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>7</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F20" s="2">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G20" s="2">
-        <v>999</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
         <v>19</v>
       </c>
-      <c r="B21" s="3">
+      <c r="B21" s="2">
         <v>2014</v>
       </c>
-      <c r="C21" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>8</v>
+      <c r="C21" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>7</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F21" s="2">
         <v>50</v>
       </c>
       <c r="G21" s="2">
-        <v>999</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
         <v>20</v>
       </c>
-      <c r="B22" s="3">
+      <c r="B22" s="2">
         <v>4001</v>
       </c>
-      <c r="C22" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>43</v>
+      <c r="C22" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F22" s="2">
         <v>98</v>
       </c>
       <c r="G22" s="2">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
         <v>21</v>
       </c>
-      <c r="B23" s="3">
+      <c r="B23" s="2">
         <v>4002</v>
       </c>
-      <c r="C23" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>43</v>
+      <c r="C23" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F23" s="2">
         <v>98</v>
       </c>
       <c r="G23" s="2">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
         <v>22</v>
       </c>
-      <c r="B24" s="3">
+      <c r="B24" s="2">
         <v>4003</v>
       </c>
-      <c r="C24" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>43</v>
+      <c r="C24" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F24" s="2">
         <v>98</v>
       </c>
       <c r="G24" s="2">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" s="1">
         <v>23</v>
       </c>
-      <c r="B25" s="3">
+      <c r="B25" s="2">
         <v>4004</v>
       </c>
-      <c r="C25" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>43</v>
+      <c r="C25" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F25" s="2">
         <v>198</v>
       </c>
       <c r="G25" s="2">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" s="1">
         <v>24</v>
       </c>
-      <c r="B26" s="3">
+      <c r="B26" s="2">
         <v>4005</v>
       </c>
-      <c r="C26" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>43</v>
+      <c r="C26" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F26" s="2">
         <v>198</v>
       </c>
       <c r="G26" s="2">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" s="1">
         <v>25</v>
       </c>
-      <c r="B27" s="3">
+      <c r="B27" s="2">
         <v>4006</v>
       </c>
-      <c r="C27" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>43</v>
+      <c r="C27" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F27" s="2">
         <v>198</v>
       </c>
       <c r="G27" s="2">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" s="1">
         <v>26</v>
       </c>
-      <c r="B28" s="3">
+      <c r="B28" s="2">
         <v>4007</v>
       </c>
-      <c r="C28" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>43</v>
+      <c r="C28" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F28" s="2">
         <v>998</v>
@@ -1213,17 +1211,17 @@
       <c r="A29" s="1">
         <v>27</v>
       </c>
-      <c r="B29" s="3">
+      <c r="B29" s="2">
         <v>4008</v>
       </c>
-      <c r="C29" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>43</v>
+      <c r="C29" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F29" s="2">
         <v>998</v>
@@ -1236,17 +1234,17 @@
       <c r="A30" s="1">
         <v>28</v>
       </c>
-      <c r="B30" s="3">
+      <c r="B30" s="2">
         <v>4009</v>
       </c>
-      <c r="C30" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>43</v>
+      <c r="C30" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F30" s="2">
         <v>998</v>
@@ -1259,17 +1257,17 @@
       <c r="A31" s="1">
         <v>29</v>
       </c>
-      <c r="B31" s="3">
+      <c r="B31" s="2">
         <v>4010</v>
       </c>
-      <c r="C31" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>43</v>
+      <c r="C31" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F31" s="2">
         <v>1980</v>
@@ -1282,17 +1280,17 @@
       <c r="A32" s="1">
         <v>30</v>
       </c>
-      <c r="B32" s="3">
+      <c r="B32" s="2">
         <v>4011</v>
       </c>
-      <c r="C32" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>43</v>
+      <c r="C32" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F32" s="2">
         <v>1980</v>
@@ -1305,17 +1303,17 @@
       <c r="A33" s="1">
         <v>31</v>
       </c>
-      <c r="B33" s="3">
+      <c r="B33" s="2">
         <v>4012</v>
       </c>
-      <c r="C33" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>43</v>
+      <c r="C33" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F33" s="2">
         <v>1980</v>
@@ -1325,6 +1323,11 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A2:G2" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:G33">
+      <sortCondition ref="A2"/>
+    </sortState>
+  </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
